--- a/examples/enset/modele-u3.xlsx
+++ b/examples/enset/modele-u3.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>publications :: classe_a_plus</t>
+          <t>prix_distinctions :: prix</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>publications :: classe_a</t>
+          <t>publications :: classe_a_plus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>publications :: classe_b</t>
+          <t>publications :: classe_a</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>publications :: classe_c</t>
+          <t>publications :: classe_b</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -555,82 +555,89 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>communications :: intl_indexee_scopus_wos</t>
+          <t>publications :: classe_c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="D7" t="inlineStr">
         <is>
-          <t>communications :: intl_referencee</t>
+          <t>communications :: intl_indexee_scopus_wos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="D8" t="inlineStr">
         <is>
-          <t>communications :: intl_non_classee</t>
+          <t>communications :: intl_referencee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="D9" t="inlineStr">
         <is>
-          <t>communications :: nationale</t>
+          <t>communications :: intl_non_classee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="D10" t="inlineStr">
         <is>
-          <t>encadrement_doctoral :: directeur_these_soutenue</t>
+          <t>communications :: nationale</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="D11" t="inlineStr">
         <is>
-          <t>encadrement_doctoral :: co_directeur_these_soutenue</t>
+          <t>encadrement_doctoral :: directeur_these_soutenue</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="D12" t="inlineStr">
         <is>
-          <t>encadrement_doctoral :: jury_soutenance</t>
+          <t>encadrement_doctoral :: co_directeur_these_soutenue</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="D13" t="inlineStr">
         <is>
-          <t>encadrement_master :: memoire_master</t>
+          <t>encadrement_doctoral :: jury_soutenance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="D14" t="inlineStr">
         <is>
-          <t>encadrement_licence :: sujet_licence</t>
+          <t>encadrement_master :: memoire_master</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="D15" t="inlineStr">
         <is>
-          <t>elearning :: cours</t>
+          <t>encadrement_licence :: sujet_licence</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="D16" t="inlineStr">
         <is>
-          <t>elearning :: td</t>
+          <t>elearning :: cours</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="D17" t="inlineStr">
+        <is>
+          <t>elearning :: td</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
         <is>
           <t>elearning :: tp</t>
         </is>
@@ -647,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,7 +667,7 @@
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
     <col width="32" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
@@ -671,21 +678,20 @@
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="32" customWidth="1" min="20" max="20"/>
     <col width="32" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
-    <col width="31" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
     <col width="32" customWidth="1" min="24" max="24"/>
     <col width="32" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="23" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="30" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="32" customWidth="1" min="29" max="29"/>
     <col width="32" customWidth="1" min="30" max="30"/>
     <col width="32" customWidth="1" min="31" max="31"/>
-    <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
-    <col width="24" customWidth="1" min="34" max="34"/>
-    <col width="20" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,137 +747,132 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>prix_distinctions (Oui/Non)</t>
+          <t>projet_international.projet_intl (qte)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>projet_international.projet_intl (qte)</t>
+          <t>projet_national.projet_national (qte)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>projet_national.projet_national (qte)</t>
+          <t>encadrement_arrete_1275.projet_1275 (qte)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>encadrement_arrete_1275.projet_1275 (qte)</t>
+          <t>encadrement_projet_labelise.projet_labelise (qte)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>encadrement_projet_labelise (Oui/Non)</t>
+          <t>cours_tronc_commun.cours_tc (qte)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>cours_tronc_commun.cours_tc (qte)</t>
+          <t>expertise_reviewing.revue_a_plus (qte)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>expertise_reviewing.revue_a_plus (qte)</t>
+          <t>expertise_reviewing.revue_a (qte)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>expertise_reviewing.revue_a (qte)</t>
+          <t>expertise_reviewing.revue_b (qte)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>expertise_reviewing.revue_b (qte)</t>
+          <t>expertise_reviewing.revue_c (qte)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>expertise_reviewing.revue_c (qte)</t>
+          <t>structures_accompagnement.attestation (qte)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>structures_accompagnement.attestation (qte)</t>
+          <t>citations_scopus.citation (qte)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>citations_scopus.citation (qte)</t>
+          <t>citations_scopus (url profil)</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>citations_scopus (url profil)</t>
+          <t>polycopie_pedagogique (Oui/Non)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>polycopie_pedagogique (Oui/Non)</t>
+          <t>polycopie_pedagogique (bonus 1 Oui/Non)</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>polycopie_pedagogique (bonus 1 Oui/Non)</t>
+          <t>polycopie_pedagogique (bonus 2 Oui/Non)</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>polycopie_pedagogique (bonus 2 Oui/Non)</t>
+          <t>chapterbook (Oui/Non)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>chapterbook (Oui/Non)</t>
+          <t>livre_isbn (Oui/Non)</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>livre_isbn (Oui/Non)</t>
+          <t>livre_isbn (bonus 1 Oui/Non)</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>livre_isbn (bonus 1 Oui/Non)</t>
+          <t>responsabilites_scientifiques.membre_conseil (qte)</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>responsabilites_scientifiques.membre_conseil (qte)</t>
+          <t>responsabilites_scientifiques.president_instance (qte)</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>responsabilites_scientifiques.president_instance (qte)</t>
+          <t>responsabilites_scientifiques.editeur (qte)</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>responsabilites_scientifiques.editeur (qte)</t>
+          <t>poste_superieur (Oui/Non)</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>poste_superieur (Oui/Non)</t>
+          <t>montant_indemnite (DA)</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>montant_indemnite (DA)</t>
+          <t>billet_estime (DA)</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>billet_estime (DA)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
           <t>frais_divers (DA)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$A$2:$A$2</formula1>
     </dataValidation>
@@ -884,10 +885,7 @@
     <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Listes!$C$2:$C$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="X2:X500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -905,10 +903,7 @@
     <dataValidation sqref="AB2:AB500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Listes!$C$2:$C$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="AG2:AG500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AF2:AF500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -986,7 +981,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Listes!$D$2:$D$17</formula1>
+      <formula1>=Listes!$D$2:$D$18</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1139,17 +1134,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>count</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Candidats</t>
+          <t>Activites</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10 pts</t>
+          <t>prix=10/u (max 10 pts)</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1210,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Projet international</t>
+          <t>Projet international (en cours)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1242,7 +1237,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Projet techno avec partenaire socio-économique / projet PNR-PRFU</t>
+          <t>Projet national techno avec partenaire socio-économique / projet PNR-PRFU (en cours)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1328,7 +1323,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>count</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1338,7 +1333,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5 pts</t>
+          <t>projet_labelise=5/u (max 5 pts)</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1345,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Encadrement master</t>
+          <t>Encadrement master (ou équivalent BAC+5 - PES)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1485,7 +1480,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Citations Scopus de l'établissement (nombre depuis le dernier bénéfice + URL du profil Scopus / Google Scholar)</t>
+          <t>Citations Scopus de l'établissement (nombre depuis le dernier bénéfice)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1647,7 +1642,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Poste supérieur</t>
+          <t>Poste supérieur (structurel / fonctionnel)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
